--- a/cet4/result/83_重生商女_职场逆袭的传奇/83_重生商女_职场逆袭的传奇_学习版.xlsx
+++ b/cet4/result/83_重生商女_职场逆袭的传奇/83_重生商女_职场逆袭的传奇_学习版.xlsx
@@ -399,724 +399,724 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>immediate</v>
       </c>
       <c r="B2" t="str">
-        <v>immediate</v>
+        <v>/ɪˈmiːdiət/</v>
       </c>
       <c r="C2" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>立即的</v>
       </c>
-      <c r="D2" t="str">
-        <v>immediate(立即的)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>eliminate</v>
       </c>
       <c r="B3" t="str">
-        <v>eliminate</v>
+        <v>/ɪˈlɪmɪneɪt/</v>
       </c>
       <c r="C3" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D3" t="str">
         <v>消除</v>
       </c>
-      <c r="D3" t="str">
-        <v>eliminate(消除)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>radish</v>
       </c>
       <c r="B4" t="str">
-        <v>radish</v>
+        <v>/ˈrædɪʃ/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>萝卜</v>
       </c>
-      <c r="D4" t="str">
-        <v>radish(萝卜)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>wife</v>
       </c>
       <c r="B5" t="str">
-        <v>wife</v>
+        <v>/waɪf/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>妻子</v>
       </c>
-      <c r="D5" t="str">
-        <v>wife(妻子)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>management</v>
       </c>
       <c r="B6" t="str">
-        <v>management</v>
+        <v>/ˈmænɪdʒmənt/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>管理</v>
       </c>
-      <c r="D6" t="str">
-        <v>management(管理)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>star</v>
       </c>
       <c r="B7" t="str">
-        <v>star</v>
+        <v>/stɑːr/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>明星</v>
       </c>
-      <c r="D7" t="str">
-        <v>star(明星)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>American</v>
       </c>
       <c r="B8" t="str">
-        <v>American</v>
+        <v>/əˈmerɪkən/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>美国的</v>
       </c>
-      <c r="D8" t="str">
-        <v>American(美国的)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>tank</v>
       </c>
       <c r="B9" t="str">
-        <v>tank</v>
+        <v>/tæŋk/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D9" t="str">
         <v>坦克</v>
       </c>
-      <c r="D9" t="str">
-        <v>tank(坦克)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>alphabet</v>
       </c>
       <c r="B10" t="str">
-        <v>alphabet</v>
+        <v>/ˈælfəbet/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>字母表</v>
       </c>
-      <c r="D10" t="str">
-        <v>alphabet(字母表)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>radium</v>
       </c>
       <c r="B11" t="str">
-        <v>radium</v>
+        <v>/ˈreɪdiəm/</v>
       </c>
       <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>镭</v>
       </c>
-      <c r="D11" t="str">
-        <v>radium(镭)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>unity</v>
       </c>
       <c r="B12" t="str">
-        <v>unity</v>
+        <v>/ˈjuːnəti/</v>
       </c>
       <c r="C12" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>团结</v>
       </c>
-      <c r="D12" t="str">
-        <v>unity(团结)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>shine</v>
       </c>
       <c r="B13" t="str">
-        <v>shine</v>
+        <v>/ʃaɪn/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt./v.</v>
+      </c>
+      <c r="D13" t="str">
         <v>发光</v>
       </c>
-      <c r="D13" t="str">
-        <v>shine(发光)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>do</v>
       </c>
       <c r="B14" t="str">
-        <v>do</v>
+        <v>/duː; də; dʊ/</v>
       </c>
       <c r="C14" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D14" t="str">
         <v>做</v>
       </c>
-      <c r="D14" t="str">
-        <v>do(做)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>musician</v>
       </c>
       <c r="B15" t="str">
-        <v>musician</v>
+        <v>/mjuˈzɪʃn/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>音乐家</v>
       </c>
-      <c r="D15" t="str">
-        <v>musician(音乐家)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>each</v>
       </c>
       <c r="B16" t="str">
-        <v>each</v>
+        <v>/iːtʃ/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./v./adj./adv./pron.</v>
+      </c>
+      <c r="D16" t="str">
         <v>每个</v>
       </c>
-      <c r="D16" t="str">
-        <v>each(每个)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>strict</v>
       </c>
       <c r="B17" t="str">
-        <v>strict</v>
+        <v>/strɪkt/</v>
       </c>
       <c r="C17" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>严格</v>
       </c>
-      <c r="D17" t="str">
-        <v>strict(严格)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>occasional</v>
       </c>
       <c r="B18" t="str">
-        <v>occasional</v>
+        <v>/əˈkeɪʒənl/</v>
       </c>
       <c r="C18" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D18" t="str">
         <v>偶尔的</v>
       </c>
-      <c r="D18" t="str">
-        <v>occasional(偶尔的)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>instant</v>
       </c>
       <c r="B19" t="str">
-        <v>instant</v>
+        <v>/ˈɪnstənt/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>即时</v>
       </c>
-      <c r="D19" t="str">
-        <v>instant(即时)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>initial</v>
       </c>
       <c r="B20" t="str">
-        <v>initial</v>
+        <v>/ɪˈnɪʃl/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>最初的</v>
       </c>
-      <c r="D20" t="str">
-        <v>initial(最初的)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>speaker</v>
       </c>
       <c r="B21" t="str">
-        <v>speaker</v>
+        <v>/ˈspiːkər/</v>
       </c>
       <c r="C21" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>演讲者</v>
       </c>
-      <c r="D21" t="str">
-        <v>speaker(演讲者)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>awful</v>
       </c>
       <c r="B22" t="str">
-        <v>awful</v>
+        <v>/ˈɔːfl/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D22" t="str">
         <v>极好的</v>
       </c>
-      <c r="D22" t="str">
-        <v>awful(极好的)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>security</v>
       </c>
       <c r="B23" t="str">
-        <v>security</v>
+        <v>/sɪˈkjʊrəti/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>安全</v>
       </c>
-      <c r="D23" t="str">
-        <v>security(安全)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>electron</v>
       </c>
       <c r="B24" t="str">
-        <v>electron</v>
+        <v>/ɪˈlektrɑːn/</v>
       </c>
       <c r="C24" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>电子</v>
       </c>
-      <c r="D24" t="str">
-        <v>electron(电子)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>polite</v>
       </c>
       <c r="B25" t="str">
-        <v>polite</v>
+        <v>/pəˈlaɪt/</v>
       </c>
       <c r="C25" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D25" t="str">
         <v>有礼貌的</v>
       </c>
-      <c r="D25" t="str">
-        <v>polite(有礼貌的)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>maintain</v>
       </c>
       <c r="B26" t="str">
-        <v>maintain</v>
+        <v>/meɪnˈteɪn/</v>
       </c>
       <c r="C26" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D26" t="str">
         <v>维护</v>
       </c>
-      <c r="D26" t="str">
-        <v>maintain(维护)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>simply</v>
       </c>
       <c r="B27" t="str">
-        <v>simply</v>
+        <v>/ˈsɪmpli/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D27" t="str">
         <v>简直</v>
       </c>
-      <c r="D27" t="str">
-        <v>simply(简直)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>dictionary</v>
       </c>
       <c r="B28" t="str">
-        <v>dictionary</v>
+        <v>/ˈdɪkʃəneri/</v>
       </c>
       <c r="C28" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>字典</v>
       </c>
-      <c r="D28" t="str">
-        <v>dictionary(字典)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>foreign</v>
       </c>
       <c r="B29" t="str">
-        <v>foreign</v>
+        <v>/ˈfɔːrən/</v>
       </c>
       <c r="C29" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D29" t="str">
         <v>外国</v>
       </c>
-      <c r="D29" t="str">
-        <v>foreign(外国)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>raise</v>
       </c>
       <c r="B30" t="str">
-        <v>raise</v>
+        <v>/reɪz/</v>
       </c>
       <c r="C30" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D30" t="str">
         <v>提高</v>
       </c>
-      <c r="D30" t="str">
-        <v>raise(提高)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>lean</v>
       </c>
       <c r="B31" t="str">
-        <v>lean</v>
+        <v>/liːn/</v>
       </c>
       <c r="C31" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D31" t="str">
         <v>倚靠</v>
       </c>
-      <c r="D31" t="str">
-        <v>lean(倚靠)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>stool</v>
       </c>
       <c r="B32" t="str">
-        <v>stool</v>
+        <v>/stuːl/</v>
       </c>
       <c r="C32" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D32" t="str">
         <v>凳子</v>
       </c>
-      <c r="D32" t="str">
-        <v>stool(凳子)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>biology</v>
       </c>
       <c r="B33" t="str">
-        <v>biology</v>
+        <v>/baɪˈɑːlədʒi/</v>
       </c>
       <c r="C33" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>生物学</v>
       </c>
-      <c r="D33" t="str">
-        <v>biology(生物学)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>property</v>
       </c>
       <c r="B34" t="str">
-        <v>property</v>
+        <v>/ˈprɑːpərti/</v>
       </c>
       <c r="C34" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>财产</v>
       </c>
-      <c r="D34" t="str">
-        <v>property(财产)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>shelter</v>
       </c>
       <c r="B35" t="str">
-        <v>shelter</v>
+        <v>/ˈʃeltər/</v>
       </c>
       <c r="C35" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D35" t="str">
         <v>庇护所</v>
       </c>
-      <c r="D35" t="str">
-        <v>shelter(庇护所)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>arm</v>
       </c>
       <c r="B36" t="str">
-        <v>arm</v>
+        <v>/ɑːrm/</v>
       </c>
       <c r="C36" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D36" t="str">
         <v>手臂</v>
       </c>
-      <c r="D36" t="str">
-        <v>arm(手臂)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>oneself</v>
       </c>
       <c r="B37" t="str">
-        <v>oneself</v>
+        <v>/wʌnˈself/</v>
       </c>
       <c r="C37" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D37" t="str">
         <v>自己</v>
       </c>
-      <c r="D37" t="str">
-        <v>oneself(自己)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>communication</v>
       </c>
       <c r="B38" t="str">
-        <v>communication</v>
+        <v>/kəˌmjuːnɪˈkeɪʃn/</v>
       </c>
       <c r="C38" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>沟通</v>
       </c>
-      <c r="D38" t="str">
-        <v>communication(沟通)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>extraordinary</v>
       </c>
       <c r="B39" t="str">
-        <v>extraordinary</v>
+        <v>/ɪkˈstrɔːrdəneri/</v>
       </c>
       <c r="C39" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D39" t="str">
         <v>非凡的</v>
       </c>
-      <c r="D39" t="str">
-        <v>extraordinary(非凡的)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>lecture</v>
       </c>
       <c r="B40" t="str">
-        <v>lecture</v>
+        <v>/ˈlektʃər/</v>
       </c>
       <c r="C40" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D40" t="str">
         <v>讲座</v>
       </c>
-      <c r="D40" t="str">
-        <v>lecture(讲座)📢</v>
-      </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>secure</v>
       </c>
       <c r="B41" t="str">
-        <v>secure</v>
+        <v>/sɪˈkjʊr/</v>
       </c>
       <c r="C41" t="str">
+        <v>vt./vi./adj.</v>
+      </c>
+      <c r="D41" t="str">
         <v>确保</v>
       </c>
-      <c r="D41" t="str">
-        <v>secure(确保)📢</v>
-      </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>layer</v>
       </c>
       <c r="B42" t="str">
-        <v>layer</v>
+        <v>/ˈleɪər/</v>
       </c>
       <c r="C42" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>层</v>
       </c>
-      <c r="D42" t="str">
-        <v>layer(层)📢</v>
-      </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>thoughtful</v>
       </c>
       <c r="B43" t="str">
-        <v>thoughtful</v>
+        <v>/ˈθɔːtfl/</v>
       </c>
       <c r="C43" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D43" t="str">
         <v>体贴的</v>
       </c>
-      <c r="D43" t="str">
-        <v>thoughtful(体贴的)📢</v>
-      </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>include</v>
       </c>
       <c r="B44" t="str">
-        <v>include</v>
+        <v>/ɪnˈkluːd/</v>
       </c>
       <c r="C44" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D44" t="str">
         <v>包括</v>
       </c>
-      <c r="D44" t="str">
-        <v>include(包括)📢</v>
-      </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>bubble</v>
       </c>
       <c r="B45" t="str">
-        <v>bubble</v>
+        <v>/ˈbʌbl/</v>
       </c>
       <c r="C45" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D45" t="str">
         <v>泡沫</v>
       </c>
-      <c r="D45" t="str">
-        <v>bubble(泡沫)📢</v>
-      </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>swift</v>
       </c>
       <c r="B46" t="str">
-        <v>swift</v>
+        <v>/swɪft/</v>
       </c>
       <c r="C46" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D46" t="str">
         <v>迅速的</v>
       </c>
-      <c r="D46" t="str">
-        <v>swift(迅速的)📢</v>
-      </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>save</v>
       </c>
       <c r="B47" t="str">
-        <v>save</v>
+        <v>/seɪv/</v>
       </c>
       <c r="C47" t="str">
+        <v>n./vt./vi./prep.</v>
+      </c>
+      <c r="D47" t="str">
         <v>拯救</v>
       </c>
-      <c r="D47" t="str">
-        <v>save(拯救)📢</v>
-      </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>football</v>
       </c>
       <c r="B48" t="str">
-        <v>football</v>
+        <v>/ˈfʊtbɔːl/</v>
       </c>
       <c r="C48" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D48" t="str">
         <v>足球</v>
       </c>
-      <c r="D48" t="str">
-        <v>football(足球)📢</v>
-      </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>ruler</v>
       </c>
       <c r="B49" t="str">
-        <v>ruler</v>
+        <v>/ˈruːlər/</v>
       </c>
       <c r="C49" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D49" t="str">
         <v>尺</v>
       </c>
-      <c r="D49" t="str">
-        <v>ruler(尺)📢</v>
-      </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>frontier</v>
       </c>
       <c r="B50" t="str">
-        <v>frontier</v>
+        <v>/frʌnˈtɪr/</v>
       </c>
       <c r="C50" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D50" t="str">
         <v>前沿</v>
       </c>
-      <c r="D50" t="str">
-        <v>frontier(前沿)📢</v>
-      </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>tyre</v>
       </c>
       <c r="B51" t="str">
-        <v>tyre</v>
+        <v>/ˈtaɪər/</v>
       </c>
       <c r="C51" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D51" t="str">
         <v>轮胎</v>
-      </c>
-      <c r="D51" t="str">
-        <v>tyre(轮胎)📢</v>
       </c>
     </row>
   </sheetData>
